--- a/public/exports-from-60-with-coowners/29189978.xlsx
+++ b/public/exports-from-60-with-coowners/29189978.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000942</t>
+          <t xml:space="preserve">310000943</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294470</t>
+          <t xml:space="preserve">311294471</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294461</t>
+          <t xml:space="preserve">311294465</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189978.xlsx
+++ b/public/exports-from-60-with-coowners/29189978.xlsx
@@ -2291,26 +2291,26 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frellingvej 8</t>
+          <t xml:space="preserve">Galgebakken 4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">10043845</t>
+          <t xml:space="preserve">741598, 5618733</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J31">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Galgebakken 4</t>
+          <t xml:space="preserve">Gråskegårdevej 2B</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">741598, 5618733</t>
+          <t xml:space="preserve">9154991</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="J32">
-        <v>138</v>
+        <v>948</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gråskegårdevej 2B</t>
+          <t xml:space="preserve">Havnevej 15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2451,16 +2451,16 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">9154991</t>
+          <t xml:space="preserve">9787579</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J33">
-        <v>948</v>
+        <v>97</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havnevej 15</t>
+          <t xml:space="preserve">Hybenbakken 1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2526,16 +2526,16 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">9787579</t>
+          <t xml:space="preserve">4177567</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J34">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2591,17 +2591,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hybenbakken 1</t>
+          <t xml:space="preserve">Industrivej 21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">4177567</t>
+          <t xml:space="preserve">8925031</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="J35">
-        <v>152</v>
+        <v>1047</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2666,26 +2666,26 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrivej 21</t>
+          <t xml:space="preserve">Kirkevej 13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">8925031</t>
+          <t xml:space="preserve">4151141</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">25</t>
         </is>
       </c>
       <c r="J36">
-        <v>1047</v>
+        <v>333</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2741,26 +2741,26 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 13</t>
+          <t xml:space="preserve">Knebel Bygade 31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151141</t>
+          <t xml:space="preserve">4165334</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J37">
-        <v>333</v>
+        <v>138</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knebel Bygade 31</t>
+          <t xml:space="preserve">Lyngevej 5I</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2826,16 +2826,16 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165334</t>
+          <t xml:space="preserve">1450847</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J38">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5I</t>
+          <t xml:space="preserve">Lyngevej 5K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J39">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5K</t>
+          <t xml:space="preserve">Lyngevej 5M</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J40">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5M</t>
+          <t xml:space="preserve">Lyngevej 5O</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J41">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5O</t>
+          <t xml:space="preserve">Lyngevej 7O</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3126,16 +3126,16 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1450847</t>
+          <t xml:space="preserve">8124496</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J42">
-        <v>120</v>
+        <v>490</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 7O</t>
+          <t xml:space="preserve">Lyngevej 9I</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3201,16 +3201,16 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">8124496</t>
+          <t xml:space="preserve">9835515</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J43">
-        <v>490</v>
+        <v>207</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 9I</t>
+          <t xml:space="preserve">Lyngevej 9M</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J44">
@@ -3341,26 +3341,26 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 9M</t>
+          <t xml:space="preserve">Maarupvej 5A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835515</t>
+          <t xml:space="preserve">4174157</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J45">
-        <v>207</v>
+        <v>124</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maarupvej 5A</t>
+          <t xml:space="preserve">Maarupvej 5B</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3431,11 +3431,11 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J46">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3491,26 +3491,26 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maarupvej 5B</t>
+          <t xml:space="preserve">Marienhoffvej 13B</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">4174157</t>
+          <t xml:space="preserve">100168061</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J47">
-        <v>174</v>
+        <v>2103</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienhoffvej 13B</t>
+          <t xml:space="preserve">Marienhoffvej 13C</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3576,16 +3576,16 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">100168061</t>
+          <t xml:space="preserve">741660, 100168061</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J48">
-        <v>2103</v>
+        <v>833</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3656,11 +3656,11 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J49">
-        <v>833</v>
+        <v>144</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienhoffvej 13C</t>
+          <t xml:space="preserve">Marienhoffvej 13D</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3726,16 +3726,16 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">741660, 100168061</t>
+          <t xml:space="preserve">100168061</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J50">
-        <v>144</v>
+        <v>699</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -3791,26 +3791,26 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienhoffvej 13D</t>
+          <t xml:space="preserve">Mols Bjerge Vej 8A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">100168061</t>
+          <t xml:space="preserve">100276231</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J51">
-        <v>699</v>
+        <v>105</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -3866,26 +3866,26 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mols Bjerge Vej 8A</t>
+          <t xml:space="preserve">Nimtoftevej 12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">100276231</t>
+          <t xml:space="preserve">9994014</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J52">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nimtoftevej 12</t>
+          <t xml:space="preserve">Nordre Ringvej 9L</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3951,16 +3951,16 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">9994014</t>
+          <t xml:space="preserve">4124915</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J53">
-        <v>120</v>
+        <v>231</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4016,26 +4016,26 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 9L</t>
+          <t xml:space="preserve">Nørrealle 4B</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124915</t>
+          <t xml:space="preserve">5617732</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J54">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4091,17 +4091,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrealle 4B</t>
+          <t xml:space="preserve">Pollen 2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617732</t>
+          <t xml:space="preserve">4117377</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="J55">
-        <v>330</v>
+        <v>300</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4166,26 +4166,26 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pollen 2</t>
+          <t xml:space="preserve">Rodskovvej 58</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">4117377</t>
+          <t xml:space="preserve">100465851</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J56">
-        <v>300</v>
+        <v>1030</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4241,26 +4241,26 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodskovvej 58</t>
+          <t xml:space="preserve">S.A. Jensens Vej 3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">100465851</t>
+          <t xml:space="preserve">5617326</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J57">
-        <v>1030</v>
+        <v>374</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.A. Jensens Vej 3</t>
+          <t xml:space="preserve">S.A. Jensens Vej 4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -4326,16 +4326,16 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617326</t>
+          <t xml:space="preserve">741623, 5617339</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J58">
-        <v>374</v>
+        <v>320</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4406,11 +4406,11 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J59">
-        <v>320</v>
+        <v>1142</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4481,11 +4481,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J60">
-        <v>1142</v>
+        <v>1930</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4541,17 +4541,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.A. Jensens Vej 4</t>
+          <t xml:space="preserve">Sandballevej 5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">741623, 5617339</t>
+          <t xml:space="preserve">10033354</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="J61">
-        <v>1930</v>
+        <v>274</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4616,26 +4616,26 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandballevej 5</t>
+          <t xml:space="preserve">Skansevej 6</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">10033354</t>
+          <t xml:space="preserve">741613, 5618633</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J62">
-        <v>274</v>
+        <v>70</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -4691,17 +4691,17 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skansevej 6</t>
+          <t xml:space="preserve">Skoletoften 17A</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">741613, 5618633</t>
+          <t xml:space="preserve">4165337</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="J63">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4766,26 +4766,26 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 17A</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165337</t>
+          <t xml:space="preserve">4123748</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J64">
-        <v>68</v>
+        <v>250</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -4841,26 +4841,26 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Skolevej 10</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123748</t>
+          <t xml:space="preserve">100625342</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J65">
-        <v>250</v>
+        <v>804</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -4916,26 +4916,26 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 10</t>
+          <t xml:space="preserve">Skolevej 12</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">100625342</t>
+          <t xml:space="preserve">8587308</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J66">
-        <v>804</v>
+        <v>1111</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4991,17 +4991,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 12</t>
+          <t xml:space="preserve">Skovbakkevej 15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">8587308</t>
+          <t xml:space="preserve">741676, 4123019</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5010,7 +5010,7 @@
         </is>
       </c>
       <c r="J67">
-        <v>1111</v>
+        <v>425</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5066,17 +5066,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovbakkevej 15</t>
+          <t xml:space="preserve">Skovvænget 3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">741676, 4123019</t>
+          <t xml:space="preserve">741614, 1452032</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="J68">
-        <v>425</v>
+        <v>93</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5141,26 +5141,26 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 3</t>
+          <t xml:space="preserve">Skrejrupvej 3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">741614, 1452032</t>
+          <t xml:space="preserve">4141159</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J69">
-        <v>93</v>
+        <v>174</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrejrupvej 3</t>
+          <t xml:space="preserve">Skrejrupvej 9B</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5226,16 +5226,16 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141159</t>
+          <t xml:space="preserve">4141177</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J70">
-        <v>174</v>
+        <v>3262</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5291,26 +5291,26 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrejrupvej 9B</t>
+          <t xml:space="preserve">Skudehavnen 2A</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141177</t>
+          <t xml:space="preserve">5619163</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J71">
-        <v>3262</v>
+        <v>110</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skudehavnen 2A</t>
+          <t xml:space="preserve">Skudehavnen 2B</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -5376,16 +5376,16 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">5619163</t>
+          <t xml:space="preserve">741658, 10136366</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J72">
-        <v>110</v>
+        <v>358</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skudehavnen 2B</t>
+          <t xml:space="preserve">Skudehavnen 61</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -5451,16 +5451,16 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">741658, 10136366</t>
+          <t xml:space="preserve">741612, 5619163</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J73">
-        <v>358</v>
+        <v>160</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skudehavnen 61</t>
+          <t xml:space="preserve">Skudehavnen 62</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5531,11 +5531,11 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J74">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5591,26 +5591,26 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skudehavnen 62</t>
+          <t xml:space="preserve">Sognevejen 15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">741612, 5619163</t>
+          <t xml:space="preserve">4176129</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J75">
-        <v>185</v>
+        <v>89</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5666,26 +5666,26 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sognevejen 15</t>
+          <t xml:space="preserve">Stadionvej 25</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">4176129</t>
+          <t xml:space="preserve">7811024</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J76">
-        <v>89</v>
+        <v>254</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5756,11 +5756,11 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J77">
-        <v>254</v>
+        <v>115</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5831,11 +5831,11 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J78">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 25</t>
+          <t xml:space="preserve">Stadionvej 27</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5906,11 +5906,11 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J79">
-        <v>105</v>
+        <v>240</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 27</t>
+          <t xml:space="preserve">Stadionvej 4A</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5976,16 +5976,16 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">7811024</t>
+          <t xml:space="preserve">101001610, 101001611</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J80">
-        <v>240</v>
+        <v>4075</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6041,26 +6041,26 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 4A</t>
+          <t xml:space="preserve">Stockflethsvej 12</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">101001610, 101001611</t>
+          <t xml:space="preserve">741594, 9787579</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J81">
-        <v>4075</v>
+        <v>500</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 12</t>
+          <t xml:space="preserve">Stockflethsvej 13B</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6126,16 +6126,16 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">741594, 9787579</t>
+          <t xml:space="preserve">741593, 10136366</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J82">
-        <v>500</v>
+        <v>253</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 13B</t>
+          <t xml:space="preserve">Stockflethsvej 19</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -6201,16 +6201,16 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">741593, 10136366</t>
+          <t xml:space="preserve">741602, 9787579</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="J83">
-        <v>253</v>
+        <v>60</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 19</t>
+          <t xml:space="preserve">Stockflethsvej 8</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -6276,16 +6276,16 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">741602, 9787579</t>
+          <t xml:space="preserve">741590, 9787579</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J84">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stockflethsvej 8</t>
+          <t xml:space="preserve">Strandvejen 8</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -6351,16 +6351,16 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">741590, 9787579</t>
+          <t xml:space="preserve">5617299</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J85">
-        <v>220</v>
+        <v>439</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6416,26 +6416,26 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 8</t>
+          <t xml:space="preserve">Tingvej 18A</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617299</t>
+          <t xml:space="preserve">4148917</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J86">
-        <v>439</v>
+        <v>245</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 18A</t>
+          <t xml:space="preserve">Toftevej 6</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148917</t>
+          <t xml:space="preserve">741673, 4148613</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="J87">
-        <v>245</v>
+        <v>180</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -6566,17 +6566,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Toftevej 6</t>
+          <t xml:space="preserve">Tørvevej 2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">741673, 4148613</t>
+          <t xml:space="preserve">10050357</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="J88">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tørvevej 2</t>
+          <t xml:space="preserve">Tørvevej 4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050357</t>
+          <t xml:space="preserve">10050356</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -6660,7 +6660,7 @@
         </is>
       </c>
       <c r="J89">
-        <v>170</v>
+        <v>86</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tørvevej 4</t>
+          <t xml:space="preserve">Vestergade 116A</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -6726,16 +6726,16 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">10050356</t>
+          <t xml:space="preserve">4123336</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J90">
-        <v>86</v>
+        <v>232</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -6791,26 +6791,26 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 116A</t>
+          <t xml:space="preserve">Vestervej 15</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123336</t>
+          <t xml:space="preserve">10136366</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J91">
-        <v>232</v>
+        <v>376</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 15</t>
+          <t xml:space="preserve">Vestervej 17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6881,11 +6881,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J92">
-        <v>376</v>
+        <v>547</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 17</t>
+          <t xml:space="preserve">Vestervej 19</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6956,11 +6956,11 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J93">
-        <v>547</v>
+        <v>450</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7016,7 +7016,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 19</t>
+          <t xml:space="preserve">Vestervej 9</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7026,16 +7026,16 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">10136366</t>
+          <t xml:space="preserve">9926304</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J94">
-        <v>450</v>
+        <v>233</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7091,26 +7091,26 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 9</t>
+          <t xml:space="preserve">Ådalen 20B</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926304</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J95">
-        <v>233</v>
+        <v>79</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalen 20B</t>
+          <t xml:space="preserve">Ådalen 2B</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7176,16 +7176,16 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">741674, 4126345</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J96">
-        <v>79</v>
+        <v>1893</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalen 2B</t>
+          <t xml:space="preserve">Ådalen 2D</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7251,16 +7251,16 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">741674, 4126345</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J97">
-        <v>1893</v>
+        <v>141</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7316,26 +7316,26 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalen 2D</t>
+          <t xml:space="preserve">Ågårdvej 2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">9888746</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J98">
-        <v>141</v>
+        <v>309</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdvej 2</t>
+          <t xml:space="preserve">Ågårdvej 3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7401,16 +7401,16 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">9888746</t>
+          <t xml:space="preserve">9516512</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J99">
-        <v>309</v>
+        <v>129</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7466,7 +7466,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdvej 3</t>
+          <t xml:space="preserve">Ågårdvej 52</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7476,16 +7476,16 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">9516512</t>
+          <t xml:space="preserve">1449915</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J100">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
@@ -7541,26 +7541,26 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdvej 52</t>
+          <t xml:space="preserve">Århusvej 27</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1449915</t>
+          <t xml:space="preserve">4152244</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J101">
-        <v>166</v>
+        <v>79</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -7631,11 +7631,11 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J102">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7706,11 +7706,11 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J103">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7766,26 +7766,26 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 27</t>
+          <t xml:space="preserve">Østeralle 19B</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t xml:space="preserve">4152244</t>
+          <t xml:space="preserve">8708759</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J104">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7841,7 +7841,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østeralle 19B</t>
+          <t xml:space="preserve">Østeralle 35</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -7851,16 +7851,16 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708759</t>
+          <t xml:space="preserve">7877946</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J105">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østeralle 35</t>
+          <t xml:space="preserve">Østeralle 9</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -7926,16 +7926,16 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t xml:space="preserve">7877946</t>
+          <t xml:space="preserve">5617675</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J106">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -7991,45 +7991,45 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østeralle 9</t>
+          <t xml:space="preserve">Skolevangen 2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617675</t>
+          <t xml:space="preserve">4148710</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J107">
-        <v>62</v>
+        <v>185</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">200013425</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Just A/S</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2019-05-07</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mangler energimærke</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O107" t="inlineStr">
@@ -8066,17 +8066,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 2</t>
+          <t xml:space="preserve">Bugtrupvej 25</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148710</t>
+          <t xml:space="preserve">4173794</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8085,11 +8085,11 @@
         </is>
       </c>
       <c r="J108">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013425</t>
+          <t xml:space="preserve">200013754</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-07</t>
+          <t xml:space="preserve">2019-05-15</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8141,17 +8141,17 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 25</t>
+          <t xml:space="preserve">Hornbjergvej 17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173794</t>
+          <t xml:space="preserve">4150191</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8160,11 +8160,11 @@
         </is>
       </c>
       <c r="J109">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">200013754</t>
+          <t xml:space="preserve">200014249</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-15</t>
+          <t xml:space="preserve">2019-05-28</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8216,17 +8216,17 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hornbjergvej 17</t>
+          <t xml:space="preserve">Gransvinget 67</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t xml:space="preserve">4150191</t>
+          <t xml:space="preserve">8122210</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8235,11 +8235,11 @@
         </is>
       </c>
       <c r="J110">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014249</t>
+          <t xml:space="preserve">200019155</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-05-28</t>
+          <t xml:space="preserve">2019-08-24</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gransvinget 67</t>
+          <t xml:space="preserve">Dråbyvej 9</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">8122210</t>
+          <t xml:space="preserve">9766554</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8310,11 +8310,11 @@
         </is>
       </c>
       <c r="J111">
-        <v>132</v>
+        <v>265</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019155</t>
+          <t xml:space="preserve">100132095</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-24</t>
+          <t xml:space="preserve">2019-08-28</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,30 +8366,30 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dråbyvej 9</t>
+          <t xml:space="preserve">Vestergade 116B</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">9766554</t>
+          <t xml:space="preserve">4123336</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t xml:space="preserve">100132095</t>
+          <t xml:space="preserve">100134164</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-28</t>
+          <t xml:space="preserve">2019-09-15</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 116B</t>
+          <t xml:space="preserve">Vestergade 116C</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -8456,15 +8456,15 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J113">
-        <v>216</v>
+        <v>168</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">100134164</t>
+          <t xml:space="preserve">200020492</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8474,7 +8474,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-15</t>
+          <t xml:space="preserve">2019-09-16</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,30 +8516,30 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 116C</t>
+          <t xml:space="preserve">Lerbakken 9</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123336</t>
+          <t xml:space="preserve">4141141</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J114">
-        <v>168</v>
+        <v>633</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020492</t>
+          <t xml:space="preserve">200020792</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-16</t>
+          <t xml:space="preserve">2019-09-21</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8591,17 +8591,17 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbakken 9</t>
+          <t xml:space="preserve">Holmbjergvej 52</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141141</t>
+          <t xml:space="preserve">4165492</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -8610,11 +8610,11 @@
         </is>
       </c>
       <c r="J115">
-        <v>633</v>
+        <v>159</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020792</t>
+          <t xml:space="preserve">200020927</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-21</t>
+          <t xml:space="preserve">2019-09-22</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,17 +8666,17 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Holmbjergvej 52</t>
+          <t xml:space="preserve">Lillerupvej 3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165492</t>
+          <t xml:space="preserve">4141749</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="J116">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200020927</t>
+          <t xml:space="preserve">100134946</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8741,17 +8741,17 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lillerupvej 3</t>
+          <t xml:space="preserve">Strandgårdshøj 48</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141749</t>
+          <t xml:space="preserve">5618657</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -8760,11 +8760,11 @@
         </is>
       </c>
       <c r="J117">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">100134946</t>
+          <t xml:space="preserve">100134994</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8816,40 +8816,40 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgårdshøj 48</t>
+          <t xml:space="preserve">Bugtrupvej 33</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618657</t>
+          <t xml:space="preserve">4173793</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J118">
-        <v>163</v>
+        <v>2569</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t xml:space="preserve">100134994</t>
+          <t xml:space="preserve">200041449</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Just A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-22</t>
+          <t xml:space="preserve">2020-11-21</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8891,40 +8891,40 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 33</t>
+          <t xml:space="preserve">Skovalleen 1</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173793</t>
+          <t xml:space="preserve">741584, 5619151</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J119">
-        <v>2569</v>
+        <v>865</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200041449</t>
+          <t xml:space="preserve">200047752</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Korsbæk &amp; Partnere Rådgivende ingeniørfirma KS</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-11-21</t>
+          <t xml:space="preserve">2021-04-07</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8966,40 +8966,40 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovalleen 1</t>
+          <t xml:space="preserve">Bøgevej 1</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">741584, 5619151</t>
+          <t xml:space="preserve">4123772</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J120">
-        <v>865</v>
+        <v>145</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200047752</t>
+          <t xml:space="preserve">310000470</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Korsbæk &amp; Partnere Rådgivende ingeniørfirma KS</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-04-07</t>
+          <t xml:space="preserve">2022-06-08</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgevej 1</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -9051,20 +9051,20 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123772</t>
+          <t xml:space="preserve">4123748</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J121">
-        <v>145</v>
+        <v>250</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000470</t>
+          <t xml:space="preserve">310000941</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-06-08</t>
+          <t xml:space="preserve">2022-07-04</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J122">
@@ -9139,7 +9139,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000941</t>
+          <t xml:space="preserve">310000943</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Nordre Ringvej 5</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,30 +9201,30 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123748</t>
+          <t xml:space="preserve">4125011</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J123">
-        <v>250</v>
+        <v>143</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000943</t>
+          <t xml:space="preserve">310003036</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-07-04</t>
+          <t xml:space="preserve">2022-09-01</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,40 +9266,40 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 5</t>
+          <t xml:space="preserve">Drosselvej 1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">4125011</t>
+          <t xml:space="preserve">741677, 4151548</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>143</v>
+        <v>1160</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">310003036</t>
+          <t xml:space="preserve">310034752</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Kuben Management A/S</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-09-01</t>
+          <t xml:space="preserve">2023-04-12</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9356,11 +9356,11 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J125">
-        <v>1160</v>
+        <v>393</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -9431,11 +9431,11 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J126">
-        <v>393</v>
+        <v>737</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -9491,40 +9491,40 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Drosselvej 1</t>
+          <t xml:space="preserve">Tendrup Hovvej 7A</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">741677, 4151548</t>
+          <t xml:space="preserve">100016008</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J127">
-        <v>737</v>
+        <v>551</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">310034752</t>
+          <t xml:space="preserve">311002109</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kuben Management A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-04-12</t>
+          <t xml:space="preserve">2023-06-05</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9551,12 +9551,12 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syddjurs Kommune</t>
+          <t xml:space="preserve">djursBO</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tendrup Hovvej 7A</t>
+          <t xml:space="preserve">Tendrup Møllevej 115</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">100016008</t>
+          <t xml:space="preserve">412350, 412351</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,21 +9585,21 @@
         </is>
       </c>
       <c r="J128">
-        <v>551</v>
+        <v>1793</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">311002109</t>
+          <t xml:space="preserve">311016416</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-06-05</t>
+          <t xml:space="preserve">2023-09-10</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9626,12 +9626,12 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t xml:space="preserve">djursBO</t>
+          <t xml:space="preserve">Syddjurs Kommune</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9641,30 +9641,30 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tendrup Møllevej 115</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">412350, 412351</t>
+          <t xml:space="preserve">4123748</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J129">
-        <v>1793</v>
+        <v>146</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">311016416</t>
+          <t xml:space="preserve">311079626</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t xml:space="preserve">2023-09-10</t>
+          <t xml:space="preserve">2024-10-22</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9716,40 +9716,40 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Østeralle 33</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123748</t>
+          <t xml:space="preserve">100064534</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J130">
-        <v>146</v>
+        <v>625</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">311079626</t>
+          <t xml:space="preserve">311088576</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Murbyg ApS</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-10-22</t>
+          <t xml:space="preserve">2024-12-17</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,17 +9791,17 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østeralle 33</t>
+          <t xml:space="preserve">Randersvej 22</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">100064534</t>
+          <t xml:space="preserve">1449630</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -9810,21 +9810,21 @@
         </is>
       </c>
       <c r="J131">
-        <v>625</v>
+        <v>233</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">311088576</t>
+          <t xml:space="preserve">311091512</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-12-17</t>
+          <t xml:space="preserve">2025-01-19</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Randersvej 22</t>
+          <t xml:space="preserve">Skolevej 1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">1449630</t>
+          <t xml:space="preserve">4123748</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9885,21 +9885,21 @@
         </is>
       </c>
       <c r="J132">
-        <v>233</v>
+        <v>1763</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">311091512</t>
+          <t xml:space="preserve">311199997</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t xml:space="preserve">2025-01-19</t>
+          <t xml:space="preserve">2026-09-12</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9941,17 +9941,17 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 1</t>
+          <t xml:space="preserve">Egedalsvej 7</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123748</t>
+          <t xml:space="preserve">5618905</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9960,11 +9960,11 @@
         </is>
       </c>
       <c r="J133">
-        <v>1763</v>
+        <v>606</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">311199997</t>
+          <t xml:space="preserve">311212792</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9974,17 +9974,17 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-09-12</t>
+          <t xml:space="preserve">2026-11-16</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -10016,30 +10016,30 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egedalsvej 7</t>
+          <t xml:space="preserve">Hovedgaden 10</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618905</t>
+          <t xml:space="preserve">361636</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J134">
-        <v>606</v>
+        <v>258</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212792</t>
+          <t xml:space="preserve">311212799</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10101,20 +10101,20 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">361636</t>
+          <t xml:space="preserve">361636, 361638, 361639</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J135">
-        <v>258</v>
+        <v>323</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212799</t>
+          <t xml:space="preserve">311212802</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,30 +10166,30 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 10</t>
+          <t xml:space="preserve">Hyrdebakken 2</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">361636, 361638, 361639</t>
+          <t xml:space="preserve">8034374</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J136">
-        <v>323</v>
+        <v>461</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212802</t>
+          <t xml:space="preserve">311212953</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-16</t>
+          <t xml:space="preserve">2026-11-17</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyrdebakken 2</t>
+          <t xml:space="preserve">Moesbakken 2A</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">8034374</t>
+          <t xml:space="preserve">8587307</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10260,11 +10260,11 @@
         </is>
       </c>
       <c r="J137">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">311212953</t>
+          <t xml:space="preserve">311215580</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10274,7 +10274,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-11-17</t>
+          <t xml:space="preserve">2026-12-01</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moesbakken 2A</t>
+          <t xml:space="preserve">Poppelvej 9</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8587307</t>
+          <t xml:space="preserve">4124588</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10335,11 +10335,11 @@
         </is>
       </c>
       <c r="J138">
-        <v>445</v>
+        <v>364</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215580</t>
+          <t xml:space="preserve">311216521</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-01</t>
+          <t xml:space="preserve">2026-12-07</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Poppelvej 9</t>
+          <t xml:space="preserve">Nordre Ringvej 5</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124588</t>
+          <t xml:space="preserve">4125011</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -10410,11 +10410,11 @@
         </is>
       </c>
       <c r="J139">
-        <v>364</v>
+        <v>605</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216521</t>
+          <t xml:space="preserve">311216854</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-07</t>
+          <t xml:space="preserve">2026-12-09</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,17 +10466,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 5</t>
+          <t xml:space="preserve">Falcksvej 2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4125011</t>
+          <t xml:space="preserve">4148336</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10485,21 +10485,21 @@
         </is>
       </c>
       <c r="J140">
-        <v>605</v>
+        <v>757</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311216854</t>
+          <t xml:space="preserve">311218178</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-09</t>
+          <t xml:space="preserve">2026-12-16</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Falcksvej 2</t>
+          <t xml:space="preserve">Bøgevej 1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148336</t>
+          <t xml:space="preserve">4123772</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,21 +10560,21 @@
         </is>
       </c>
       <c r="J141">
-        <v>757</v>
+        <v>445</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311218178</t>
+          <t xml:space="preserve">311219438</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-16</t>
+          <t xml:space="preserve">2026-12-22</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,17 +10616,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bøgevej 1</t>
+          <t xml:space="preserve">Eskerodvej 5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123772</t>
+          <t xml:space="preserve">4148280</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="J142">
-        <v>445</v>
+        <v>521</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219438</t>
+          <t xml:space="preserve">311219420</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Eskerodvej 5</t>
+          <t xml:space="preserve">Stadionvej 25</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -10701,7 +10701,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148280</t>
+          <t xml:space="preserve">7811024</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,11 +10710,11 @@
         </is>
       </c>
       <c r="J143">
-        <v>521</v>
+        <v>492</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219420</t>
+          <t xml:space="preserve">311219423</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 25</t>
+          <t xml:space="preserve">Ågårdvej 3</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,7 +10776,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">7811024</t>
+          <t xml:space="preserve">9516512</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -10785,11 +10785,11 @@
         </is>
       </c>
       <c r="J144">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219423</t>
+          <t xml:space="preserve">311219452</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10841,17 +10841,17 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdvej 3</t>
+          <t xml:space="preserve">Dalgårdsvej 2A</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9516512</t>
+          <t xml:space="preserve">4155496</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -10860,21 +10860,21 @@
         </is>
       </c>
       <c r="J145">
-        <v>529</v>
+        <v>353</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311219452</t>
+          <t xml:space="preserve">311231282</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026-12-22</t>
+          <t xml:space="preserve">2027-03-01</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgårdsvej 2A</t>
+          <t xml:space="preserve">Alpedalen 14</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155496</t>
+          <t xml:space="preserve">4149074</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,11 +10935,11 @@
         </is>
       </c>
       <c r="J146">
-        <v>353</v>
+        <v>389</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311231282</t>
+          <t xml:space="preserve">311249201</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-03-01</t>
+          <t xml:space="preserve">2027-05-23</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alpedalen 14</t>
+          <t xml:space="preserve">Egedalsvej 2</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4149074</t>
+          <t xml:space="preserve">5618867</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -11010,11 +11010,11 @@
         </is>
       </c>
       <c r="J147">
-        <v>389</v>
+        <v>769</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311249201</t>
+          <t xml:space="preserve">311250893</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-23</t>
+          <t xml:space="preserve">2027-05-31</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egedalsvej 2</t>
+          <t xml:space="preserve">Bagvænget 12</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618867</t>
+          <t xml:space="preserve">9926307</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,21 +11085,21 @@
         </is>
       </c>
       <c r="J148">
-        <v>769</v>
+        <v>2200</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311250893</t>
+          <t xml:space="preserve">311253872</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-05-31</t>
+          <t xml:space="preserve">2027-06-14</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,17 +11141,17 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bagvænget 12</t>
+          <t xml:space="preserve">Bugtrupvej 27</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926307</t>
+          <t xml:space="preserve">4173991</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -11160,16 +11160,16 @@
         </is>
       </c>
       <c r="J149">
-        <v>2200</v>
+        <v>6272</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253872</t>
+          <t xml:space="preserve">311253826</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -11231,11 +11231,11 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J150">
-        <v>6272</v>
+        <v>787</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
@@ -11291,30 +11291,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 27</t>
+          <t xml:space="preserve">Strandgårdshøj 46A</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173991</t>
+          <t xml:space="preserve">5618735</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J151">
-        <v>787</v>
+        <v>672</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253826</t>
+          <t xml:space="preserve">311253843</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandgårdshøj 46A</t>
+          <t xml:space="preserve">Vestervej 7</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,25 +11376,25 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618735</t>
+          <t xml:space="preserve">9926304</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J152">
-        <v>672</v>
+        <v>1282</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253843</t>
+          <t xml:space="preserve">311253876</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -11441,40 +11441,40 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestervej 7</t>
+          <t xml:space="preserve">Rosenholmvej 1</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">9926304</t>
+          <t xml:space="preserve">4148297</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>1282</v>
+        <v>1174</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311253876</t>
+          <t xml:space="preserve">311254476</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-14</t>
+          <t xml:space="preserve">2027-06-16</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 1</t>
+          <t xml:space="preserve">Rodskovvej 10A</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148297</t>
+          <t xml:space="preserve">4148190</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,11 +11535,11 @@
         </is>
       </c>
       <c r="J154">
-        <v>1174</v>
+        <v>1095</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311254476</t>
+          <t xml:space="preserve">311255745</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-16</t>
+          <t xml:space="preserve">2027-06-22</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodskovvej 10A</t>
+          <t xml:space="preserve">Rodskovvej 10B</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11606,11 +11606,11 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J155">
-        <v>1095</v>
+        <v>338</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -11666,30 +11666,30 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodskovvej 10B</t>
+          <t xml:space="preserve">Randersvej 85A</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148190</t>
+          <t xml:space="preserve">9741519</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J156">
-        <v>338</v>
+        <v>242</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311255745</t>
+          <t xml:space="preserve">311257370</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-22</t>
+          <t xml:space="preserve">2027-06-29</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Randersvej 85A</t>
+          <t xml:space="preserve">Randersvej 85B</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11756,15 +11756,15 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J157">
-        <v>242</v>
+        <v>190</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257370</t>
+          <t xml:space="preserve">311257372</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11831,15 +11831,15 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J158">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257372</t>
+          <t xml:space="preserve">311257371</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11891,30 +11891,30 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Randersvej 85B</t>
+          <t xml:space="preserve">Havagervej 2</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9741519</t>
+          <t xml:space="preserve">4165379</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J159">
-        <v>182</v>
+        <v>158</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311257371</t>
+          <t xml:space="preserve">311258641</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-06-29</t>
+          <t xml:space="preserve">2027-07-03</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11981,15 +11981,15 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J160">
-        <v>158</v>
+        <v>216</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258641</t>
+          <t xml:space="preserve">311258639</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,30 +12041,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Havagervej 2</t>
+          <t xml:space="preserve">Nyvej 3</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165379</t>
+          <t xml:space="preserve">4148947</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J161">
-        <v>216</v>
+        <v>715</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258639</t>
+          <t xml:space="preserve">311258642</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,17 +12116,17 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nyvej 3</t>
+          <t xml:space="preserve">Strandvejen 8</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148947</t>
+          <t xml:space="preserve">5617299</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -12135,11 +12135,11 @@
         </is>
       </c>
       <c r="J162">
-        <v>715</v>
+        <v>628</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258642</t>
+          <t xml:space="preserve">311258644</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strandvejen 8</t>
+          <t xml:space="preserve">Østeralle 17A</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12201,7 +12201,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617299</t>
+          <t xml:space="preserve">5617697</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -12210,11 +12210,11 @@
         </is>
       </c>
       <c r="J163">
-        <v>628</v>
+        <v>1675</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258644</t>
+          <t xml:space="preserve">311258643</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12266,17 +12266,17 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østeralle 17A</t>
+          <t xml:space="preserve">Mosevej 9</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617697</t>
+          <t xml:space="preserve">4151345</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>1675</v>
+        <v>851</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258643</t>
+          <t xml:space="preserve">311258719</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-03</t>
+          <t xml:space="preserve">2027-07-04</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,17 +12341,17 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mosevej 9</t>
+          <t xml:space="preserve">Vestergade 116A</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151345</t>
+          <t xml:space="preserve">4123336</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -12360,11 +12360,11 @@
         </is>
       </c>
       <c r="J165">
-        <v>851</v>
+        <v>970</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258719</t>
+          <t xml:space="preserve">311258741</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12416,17 +12416,17 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 116A</t>
+          <t xml:space="preserve">Engvej 24A</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4123336</t>
+          <t xml:space="preserve">4149546</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>970</v>
+        <v>275</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311258741</t>
+          <t xml:space="preserve">311280697</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-07-04</t>
+          <t xml:space="preserve">2027-10-26</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,17 +12491,17 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engvej 24A</t>
+          <t xml:space="preserve">Bispemosevej 5</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8444</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4149546</t>
+          <t xml:space="preserve">4173743</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,21 +12510,21 @@
         </is>
       </c>
       <c r="J167">
-        <v>275</v>
+        <v>5211</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311280697</t>
+          <t xml:space="preserve">311287373</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-10-26</t>
+          <t xml:space="preserve">2027-12-05</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,17 +12566,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bispemosevej 5</t>
+          <t xml:space="preserve">S.A. Jensens Vej 1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">8444</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173743</t>
+          <t xml:space="preserve">5617328</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12585,21 +12585,21 @@
         </is>
       </c>
       <c r="J168">
-        <v>5211</v>
+        <v>722</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311287373</t>
+          <t xml:space="preserve">311291350</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-05</t>
+          <t xml:space="preserve">2028-01-05</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">S.A. Jensens Vej 1</t>
+          <t xml:space="preserve">Østeralle 19</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617328</t>
+          <t xml:space="preserve">5617696</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -12660,21 +12660,21 @@
         </is>
       </c>
       <c r="J169">
-        <v>722</v>
+        <v>6275</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291350</t>
+          <t xml:space="preserve">311291465</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-05</t>
+          <t xml:space="preserve">2028-01-07</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,30 +12716,30 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østeralle 19</t>
+          <t xml:space="preserve">Maarupvej 3</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617696</t>
+          <t xml:space="preserve">4174157</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J170">
-        <v>6275</v>
+        <v>1503</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291465</t>
+          <t xml:space="preserve">311293050</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-07</t>
+          <t xml:space="preserve">2028-01-17</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,30 +12791,30 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Maarupvej 3</t>
+          <t xml:space="preserve">Kløvervangen 6A</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">4174157</t>
+          <t xml:space="preserve">4155954</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J171">
-        <v>1503</v>
+        <v>576</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293050</t>
+          <t xml:space="preserve">311294468</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-17</t>
+          <t xml:space="preserve">2028-01-25</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12881,11 +12881,11 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J172">
-        <v>576</v>
+        <v>2481</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -12956,11 +12956,11 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J173">
-        <v>2481</v>
+        <v>365</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -13031,11 +13031,11 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J174">
-        <v>365</v>
+        <v>216</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervangen 6A</t>
+          <t xml:space="preserve">Kløvervangen 6B</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13106,15 +13106,15 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J175">
-        <v>216</v>
+        <v>1214</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294468</t>
+          <t xml:space="preserve">311294471</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,30 +13166,30 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvervangen 6B</t>
+          <t xml:space="preserve">Nordre Ringvej 9K</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4155954</t>
+          <t xml:space="preserve">4124915</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J176">
-        <v>1214</v>
+        <v>2812</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294471</t>
+          <t xml:space="preserve">311294474</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 9K</t>
+          <t xml:space="preserve">Tingvej 17</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124915</t>
+          <t xml:space="preserve">4148745</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J177">
-        <v>2812</v>
+        <v>3923</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294474</t>
+          <t xml:space="preserve">311294457</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13316,30 +13316,30 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 17</t>
+          <t xml:space="preserve">Århusvej 33C</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148745</t>
+          <t xml:space="preserve">1803816</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J178">
-        <v>3923</v>
+        <v>122</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294457</t>
+          <t xml:space="preserve">311294465</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 33C</t>
+          <t xml:space="preserve">Århusvej 33H</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13406,11 +13406,11 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J179">
-        <v>122</v>
+        <v>360</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 33H</t>
+          <t xml:space="preserve">Århusvej 35</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13481,11 +13481,11 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J180">
-        <v>360</v>
+        <v>228</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 35</t>
+          <t xml:space="preserve">Skolevej 7</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13551,20 +13551,20 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803816</t>
+          <t xml:space="preserve">5617617</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J181">
-        <v>228</v>
+        <v>7166</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294465</t>
+          <t xml:space="preserve">311294654</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-25</t>
+          <t xml:space="preserve">2028-01-26</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,17 +13616,17 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 7</t>
+          <t xml:space="preserve">Lyngevej 3</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617617</t>
+          <t xml:space="preserve">8708462</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -13635,11 +13635,11 @@
         </is>
       </c>
       <c r="J182">
-        <v>7166</v>
+        <v>1466</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294654</t>
+          <t xml:space="preserve">311296511</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-26</t>
+          <t xml:space="preserve">2028-02-07</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 3</t>
+          <t xml:space="preserve">Lyngevej 7</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,20 +13701,20 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708462</t>
+          <t xml:space="preserve">8124496</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J183">
-        <v>1466</v>
+        <v>490</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296511</t>
+          <t xml:space="preserve">311296510</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13766,7 +13766,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 7</t>
+          <t xml:space="preserve">Lyngevej 7H</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J184">
@@ -13841,30 +13841,30 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 7H</t>
+          <t xml:space="preserve">Århusvej 27</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">8124496</t>
+          <t xml:space="preserve">4152244</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J185">
-        <v>490</v>
+        <v>403</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296510</t>
+          <t xml:space="preserve">311296508</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13931,11 +13931,11 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J186">
-        <v>403</v>
+        <v>463</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -14006,15 +14006,15 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J187">
-        <v>463</v>
+        <v>130</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296508</t>
+          <t xml:space="preserve">311296509</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14081,15 +14081,15 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J188">
-        <v>130</v>
+        <v>253</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296509</t>
+          <t xml:space="preserve">311296508</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -14156,11 +14156,11 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J189">
-        <v>253</v>
+        <v>83</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 27</t>
+          <t xml:space="preserve">Skrejrupvej 1</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -14226,20 +14226,20 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">4152244</t>
+          <t xml:space="preserve">4141159</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J190">
-        <v>83</v>
+        <v>2122</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311296508</t>
+          <t xml:space="preserve">311299126</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-07</t>
+          <t xml:space="preserve">2028-02-22</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14306,11 +14306,11 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J191">
-        <v>2122</v>
+        <v>640</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
@@ -14381,11 +14381,11 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J192">
-        <v>640</v>
+        <v>2258</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -14456,11 +14456,11 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J193">
-        <v>2258</v>
+        <v>3414</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -14531,11 +14531,11 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J194">
-        <v>3414</v>
+        <v>703</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrejrupvej 1</t>
+          <t xml:space="preserve">Skrejrupvej 7</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14606,11 +14606,11 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J195">
-        <v>703</v>
+        <v>691</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
@@ -14666,30 +14666,30 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrejrupvej 7</t>
+          <t xml:space="preserve">Skolevej 19</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141159</t>
+          <t xml:space="preserve">4151491</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J196">
-        <v>691</v>
+        <v>865</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311299126</t>
+          <t xml:space="preserve">311330686</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-22</t>
+          <t xml:space="preserve">2028-08-15</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,30 +14741,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 19</t>
+          <t xml:space="preserve">Nørreport 18A</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151491</t>
+          <t xml:space="preserve">5618817</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>865</v>
+        <v>1294</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311330686</t>
+          <t xml:space="preserve">311332828</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-15</t>
+          <t xml:space="preserve">2028-08-28</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 18A</t>
+          <t xml:space="preserve">Lundbergsvej 2</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -14826,7 +14826,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618817</t>
+          <t xml:space="preserve">5618414</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>1294</v>
+        <v>9380</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311332828</t>
+          <t xml:space="preserve">311339427</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-08-28</t>
+          <t xml:space="preserve">2028-10-03</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lundbergsvej 2</t>
+          <t xml:space="preserve">Nordre Ringvej 7A</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618414</t>
+          <t xml:space="preserve">4124942</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,16 +14910,16 @@
         </is>
       </c>
       <c r="J199">
-        <v>9380</v>
+        <v>430</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339427</t>
+          <t xml:space="preserve">311339459</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M199" t="inlineStr">
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 7A</t>
+          <t xml:space="preserve">Rosengården 1</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124942</t>
+          <t xml:space="preserve">7205819</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,21 +14985,21 @@
         </is>
       </c>
       <c r="J200">
-        <v>430</v>
+        <v>2019</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311339459</t>
+          <t xml:space="preserve">311340763</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-03</t>
+          <t xml:space="preserve">2028-10-10</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15056,15 +15056,15 @@
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J201">
-        <v>2019</v>
+        <v>6224</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340763</t>
+          <t xml:space="preserve">311340762</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosengården 1</t>
+          <t xml:space="preserve">Tingvej 22</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15131,15 +15131,15 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J202">
-        <v>6224</v>
+        <v>227</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340762</t>
+          <t xml:space="preserve">311340765</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 22</t>
+          <t xml:space="preserve">Kløvevej 1</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7205819</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J203">
-        <v>227</v>
+        <v>875</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311340765</t>
+          <t xml:space="preserve">311344086</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-10</t>
+          <t xml:space="preserve">2028-10-30</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,30 +15266,30 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kløvevej 1</t>
+          <t xml:space="preserve">Skoletoften 17</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">4165334</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J204">
-        <v>875</v>
+        <v>4960</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311344086</t>
+          <t xml:space="preserve">311347460</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-10-30</t>
+          <t xml:space="preserve">2028-11-19</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15356,11 +15356,11 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J205">
-        <v>4960</v>
+        <v>779</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
@@ -15401,12 +15401,12 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syddjurs Kommune</t>
+          <t xml:space="preserve">Bofællesskabet Marie Magdalene</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -15416,30 +15416,30 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 17</t>
+          <t xml:space="preserve">Vestergade 114</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165334</t>
+          <t xml:space="preserve">378675, 378676</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J206">
-        <v>779</v>
+        <v>1638</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311347460</t>
+          <t xml:space="preserve">311349195</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-19</t>
+          <t xml:space="preserve">2028-11-29</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15476,12 +15476,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bofællesskabet Marie Magdalene</t>
+          <t xml:space="preserve">Syddjurs Kommune</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -15491,17 +15491,17 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 114</t>
+          <t xml:space="preserve">Bugtrupvej 29</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">378675, 378676</t>
+          <t xml:space="preserve">4173793</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>1638</v>
+        <v>480</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311349195</t>
+          <t xml:space="preserve">311352227</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-11-29</t>
+          <t xml:space="preserve">2028-12-19</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15581,11 +15581,11 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J208">
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -15641,30 +15641,30 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 29</t>
+          <t xml:space="preserve">Ådalen 2</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173793</t>
+          <t xml:space="preserve">4126345</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J209">
-        <v>523</v>
+        <v>2790</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311352227</t>
+          <t xml:space="preserve">311354232</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15674,7 +15674,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-12-19</t>
+          <t xml:space="preserve">2029-01-10</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15731,11 +15731,11 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J210">
-        <v>2790</v>
+        <v>2973</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
@@ -15791,30 +15791,30 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalen 2</t>
+          <t xml:space="preserve">Ballesvej 6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">4126345</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J211">
-        <v>2973</v>
+        <v>3597</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311354232</t>
+          <t xml:space="preserve">311358653</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-01-10</t>
+          <t xml:space="preserve">2029-02-08</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15881,11 +15881,11 @@
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J212">
-        <v>3597</v>
+        <v>4680</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
@@ -15956,11 +15956,11 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J213">
-        <v>4680</v>
+        <v>667</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
@@ -16031,11 +16031,11 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J214">
-        <v>667</v>
+        <v>872</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballesvej 6</t>
+          <t xml:space="preserve">Skolevangen 1</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -16106,15 +16106,15 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J215">
-        <v>872</v>
+        <v>488</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358653</t>
+          <t xml:space="preserve">311358656</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16166,40 +16166,40 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevangen 1</t>
+          <t xml:space="preserve">Bugtrupvej 41</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">4173832</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J216">
-        <v>488</v>
+        <v>1068</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311358656</t>
+          <t xml:space="preserve">311364664</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Just A/S Rådgivende Ingeniørfirma</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-08</t>
+          <t xml:space="preserve">2029-03-14</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 41</t>
+          <t xml:space="preserve">Bugtrupvej 39</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16256,15 +16256,15 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J217">
-        <v>1068</v>
+        <v>1052</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311364664</t>
+          <t xml:space="preserve">311364992</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-14</t>
+          <t xml:space="preserve">2029-03-15</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,40 +16316,40 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 39</t>
+          <t xml:space="preserve">Rodskovvej 10C</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173832</t>
+          <t xml:space="preserve">4148190</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J218">
-        <v>1052</v>
+        <v>112</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311364992</t>
+          <t xml:space="preserve">311377157</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Just A/S Rådgivende Ingeniørfirma</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-03-15</t>
+          <t xml:space="preserve">2029-05-15</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodskovvej 10C</t>
+          <t xml:space="preserve">Rodskovvej 10E</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J219">
@@ -16414,7 +16414,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377157</t>
+          <t xml:space="preserve">311377159</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16466,40 +16466,40 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rodskovvej 10E</t>
+          <t xml:space="preserve">Bakkevej 4A</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148190</t>
+          <t xml:space="preserve">8124971</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J220">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311377159</t>
+          <t xml:space="preserve">311410722</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-05-15</t>
+          <t xml:space="preserve">2029-11-25</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 4A</t>
+          <t xml:space="preserve">Bakkevej 4B</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16556,15 +16556,15 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J221">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410722</t>
+          <t xml:space="preserve">311410727</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 4B</t>
+          <t xml:space="preserve">Bakkevej 4C</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J222">
@@ -16639,7 +16639,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410727</t>
+          <t xml:space="preserve">311410729</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 4C</t>
+          <t xml:space="preserve">Bakkevej 4D</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J223">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410729</t>
+          <t xml:space="preserve">311410730</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 4D</t>
+          <t xml:space="preserve">Bakkevej 4E</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16781,7 +16781,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J224">
@@ -16789,7 +16789,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410730</t>
+          <t xml:space="preserve">311410732</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16841,7 +16841,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 4E</t>
+          <t xml:space="preserve">Bakkevej 4F</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -16856,7 +16856,7 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J225">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410732</t>
+          <t xml:space="preserve">311410734</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 4F</t>
+          <t xml:space="preserve">Bakkevej 4G</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J226">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410734</t>
+          <t xml:space="preserve">311410738</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 4G</t>
+          <t xml:space="preserve">Bakkevej 4H</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17006,7 +17006,7 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J227">
@@ -17014,7 +17014,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410738</t>
+          <t xml:space="preserve">311410739</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 4H</t>
+          <t xml:space="preserve">Nørreport 24A</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -17081,7 +17081,7 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J228">
@@ -17089,7 +17089,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410739</t>
+          <t xml:space="preserve">311410741</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 24A</t>
+          <t xml:space="preserve">Nørreport 24B</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J229">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410741</t>
+          <t xml:space="preserve">311410743</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17216,7 +17216,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 24B</t>
+          <t xml:space="preserve">Nørreport 26A</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -17231,7 +17231,7 @@
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J230">
@@ -17239,7 +17239,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410743</t>
+          <t xml:space="preserve">311410745</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 26A</t>
+          <t xml:space="preserve">Nørreport 26B</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -17306,7 +17306,7 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J231">
@@ -17314,7 +17314,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410745</t>
+          <t xml:space="preserve">311410747</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 26B</t>
+          <t xml:space="preserve">Nørreport 28A</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17381,7 +17381,7 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J232">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410747</t>
+          <t xml:space="preserve">311410750</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17441,7 +17441,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 28A</t>
+          <t xml:space="preserve">Nørreport 28B</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -17456,7 +17456,7 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J233">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410750</t>
+          <t xml:space="preserve">311410752</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 28B</t>
+          <t xml:space="preserve">Nørreport 28C</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J234">
@@ -17539,7 +17539,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410752</t>
+          <t xml:space="preserve">311410753</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 28C</t>
+          <t xml:space="preserve">Nørreport 28D</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17606,7 +17606,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J235">
@@ -17614,7 +17614,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410753</t>
+          <t xml:space="preserve">311410754</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 28D</t>
+          <t xml:space="preserve">Nørreport 30A</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J236">
@@ -17689,7 +17689,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410754</t>
+          <t xml:space="preserve">311410757</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 30A</t>
+          <t xml:space="preserve">Nørreport 30B</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17756,7 +17756,7 @@
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J237">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410757</t>
+          <t xml:space="preserve">311410758</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 30B</t>
+          <t xml:space="preserve">Nørreport 30C</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17831,7 +17831,7 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J238">
@@ -17839,7 +17839,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410758</t>
+          <t xml:space="preserve">311410759</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 30C</t>
+          <t xml:space="preserve">Nørreport 30D</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17906,7 +17906,7 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J239">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410759</t>
+          <t xml:space="preserve">311410760</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 30D</t>
+          <t xml:space="preserve">Nørreport 30E</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17981,7 +17981,7 @@
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="J240">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410760</t>
+          <t xml:space="preserve">311410761</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -18041,30 +18041,30 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 30E</t>
+          <t xml:space="preserve">Lyngevej 9E</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">8124971</t>
+          <t xml:space="preserve">9835515</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">22</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J241">
-        <v>63</v>
+        <v>140</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311410761</t>
+          <t xml:space="preserve">311411360</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-25</t>
+          <t xml:space="preserve">2029-11-28</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 9E</t>
+          <t xml:space="preserve">Lyngevej 9G</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J242">
@@ -18139,7 +18139,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411360</t>
+          <t xml:space="preserve">311411362</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18191,30 +18191,30 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 9G</t>
+          <t xml:space="preserve">Marienhoffvej 11A</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835515</t>
+          <t xml:space="preserve">1447910</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J243">
-        <v>140</v>
+        <v>5629</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411362</t>
+          <t xml:space="preserve">311412947</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-11-28</t>
+          <t xml:space="preserve">2029-12-09</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,17 +18266,17 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Marienhoffvej 11A</t>
+          <t xml:space="preserve">Lufthavnsvej 17</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">1447910</t>
+          <t xml:space="preserve">4171414</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -18285,11 +18285,11 @@
         </is>
       </c>
       <c r="J244">
-        <v>5629</v>
+        <v>464</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311412947</t>
+          <t xml:space="preserve">311413089</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -18299,7 +18299,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-09</t>
+          <t xml:space="preserve">2029-12-10</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,17 +18341,17 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lufthavnsvej 17</t>
+          <t xml:space="preserve">Lindebo 1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">4171414</t>
+          <t xml:space="preserve">353477, 353478</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -18360,11 +18360,11 @@
         </is>
       </c>
       <c r="J245">
-        <v>464</v>
+        <v>815</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311413089</t>
+          <t xml:space="preserve">311413537</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-10</t>
+          <t xml:space="preserve">2029-12-12</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,17 +18416,17 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindebo 1</t>
+          <t xml:space="preserve">A. Knudsens Vej 9</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">353477, 353478</t>
+          <t xml:space="preserve">5618872</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -18435,11 +18435,11 @@
         </is>
       </c>
       <c r="J246">
-        <v>815</v>
+        <v>211</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311413537</t>
+          <t xml:space="preserve">311414292</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-12</t>
+          <t xml:space="preserve">2029-12-17</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,17 +18491,17 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. Knudsens Vej 9</t>
+          <t xml:space="preserve">Nordre Ringvej 9A</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618872</t>
+          <t xml:space="preserve">4125012</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -18510,11 +18510,11 @@
         </is>
       </c>
       <c r="J247">
-        <v>211</v>
+        <v>248</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311414292</t>
+          <t xml:space="preserve">311417160</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-12-17</t>
+          <t xml:space="preserve">2030-01-14</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 9A</t>
+          <t xml:space="preserve">Nordre Ringvej 9B</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -18581,7 +18581,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J248">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417160</t>
+          <t xml:space="preserve">311417161</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 9B</t>
+          <t xml:space="preserve">Nordre Ringvej 9C</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,12 +18651,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">4125012</t>
+          <t xml:space="preserve">4124915</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J249">
@@ -18664,7 +18664,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417161</t>
+          <t xml:space="preserve">311417162</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 9C</t>
+          <t xml:space="preserve">Nordre Ringvej 9D</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J250">
@@ -18739,7 +18739,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417162</t>
+          <t xml:space="preserve">311417163</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18791,30 +18791,30 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nordre Ringvej 9D</t>
+          <t xml:space="preserve">Skolevej 15</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">4124915</t>
+          <t xml:space="preserve">4151502</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
-        <v>248</v>
+        <v>113</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417163</t>
+          <t xml:space="preserve">311417158</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18866,17 +18866,17 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 15</t>
+          <t xml:space="preserve">Århusvej 33E</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151502</t>
+          <t xml:space="preserve">1803817</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -18885,11 +18885,11 @@
         </is>
       </c>
       <c r="J252">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417158</t>
+          <t xml:space="preserve">311417563</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-14</t>
+          <t xml:space="preserve">2030-01-16</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,7 +18941,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 33E</t>
+          <t xml:space="preserve">Århusvej 33F</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J253">
@@ -18964,7 +18964,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417563</t>
+          <t xml:space="preserve">311417562</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 33F</t>
+          <t xml:space="preserve">Århusvej 33G</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -19031,7 +19031,7 @@
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J254">
@@ -19039,7 +19039,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417562</t>
+          <t xml:space="preserve">311417560</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 33G</t>
+          <t xml:space="preserve">Århusvej 33A</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19101,30 +19101,30 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803817</t>
+          <t xml:space="preserve">1803816</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J255">
-        <v>65</v>
+        <v>142</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417560</t>
+          <t xml:space="preserve">311417751</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-16</t>
+          <t xml:space="preserve">2030-01-17</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,17 +19166,17 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Århusvej 33A</t>
+          <t xml:space="preserve">Lyngevej 9A</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1803816</t>
+          <t xml:space="preserve">4165380</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -19185,21 +19185,21 @@
         </is>
       </c>
       <c r="J256">
-        <v>142</v>
+        <v>65</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311417751</t>
+          <t xml:space="preserve">311418320</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-17</t>
+          <t xml:space="preserve">2030-01-21</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 9A</t>
+          <t xml:space="preserve">Lyngevej 9B</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -19256,7 +19256,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J257">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418320</t>
+          <t xml:space="preserve">311418322</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19316,7 +19316,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 9B</t>
+          <t xml:space="preserve">Lyngevej 9C</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J258">
@@ -19339,7 +19339,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418322</t>
+          <t xml:space="preserve">311418324</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19391,7 +19391,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 9C</t>
+          <t xml:space="preserve">Lyngevej 9D</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J259">
@@ -19414,7 +19414,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418324</t>
+          <t xml:space="preserve">311418325</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 9D</t>
+          <t xml:space="preserve">Skibsbrovej 9A</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,20 +19476,20 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4165380</t>
+          <t xml:space="preserve">4164346</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418325</t>
+          <t xml:space="preserve">311418188</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19541,7 +19541,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skibsbrovej 9A</t>
+          <t xml:space="preserve">Skibsbrovej 9B</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -19556,7 +19556,7 @@
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J261">
@@ -19564,7 +19564,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418188</t>
+          <t xml:space="preserve">311418189</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skibsbrovej 9B</t>
+          <t xml:space="preserve">Skibsbrovej 9C</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
@@ -19631,7 +19631,7 @@
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J262">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418189</t>
+          <t xml:space="preserve">311418191</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skibsbrovej 9C</t>
+          <t xml:space="preserve">Skibsbrovej 9D</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19706,7 +19706,7 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J263">
@@ -19714,7 +19714,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418191</t>
+          <t xml:space="preserve">311418194</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19766,30 +19766,30 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skibsbrovej 9D</t>
+          <t xml:space="preserve">Bakkevej 5A</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4164346</t>
+          <t xml:space="preserve">5618818</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J264">
-        <v>60</v>
+        <v>1422</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418194</t>
+          <t xml:space="preserve">311418867</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-21</t>
+          <t xml:space="preserve">2030-01-24</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 5A</t>
+          <t xml:space="preserve">Nørreport 20A</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618818</t>
+          <t xml:space="preserve">8496559</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -19860,11 +19860,11 @@
         </is>
       </c>
       <c r="J265">
-        <v>1422</v>
+        <v>728</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311418867</t>
+          <t xml:space="preserve">311419346</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-24</t>
+          <t xml:space="preserve">2030-01-28</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19916,17 +19916,17 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 20A</t>
+          <t xml:space="preserve">Bugtrupvej 35A</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">8496559</t>
+          <t xml:space="preserve">7961824</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -19935,11 +19935,11 @@
         </is>
       </c>
       <c r="J266">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311419346</t>
+          <t xml:space="preserve">311420125</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19949,7 +19949,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-28</t>
+          <t xml:space="preserve">2030-01-30</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 35A</t>
+          <t xml:space="preserve">Bugtrupvej 37</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20001,7 +20001,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t xml:space="preserve">7961824</t>
+          <t xml:space="preserve">4173832</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -20010,11 +20010,11 @@
         </is>
       </c>
       <c r="J267">
-        <v>725</v>
+        <v>453</v>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420125</t>
+          <t xml:space="preserve">311420126</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20066,30 +20066,30 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 37</t>
+          <t xml:space="preserve">Lyngevej 5R</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8420</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173832</t>
+          <t xml:space="preserve">8708462</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J268">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420126</t>
+          <t xml:space="preserve">311422782</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20099,7 +20099,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-01-30</t>
+          <t xml:space="preserve">2030-02-14</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5R</t>
+          <t xml:space="preserve">Lyngevej 5A</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20151,20 +20151,20 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">8708462</t>
+          <t xml:space="preserve">1450847</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J269">
-        <v>480</v>
+        <v>120</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311422782</t>
+          <t xml:space="preserve">311423046</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-14</t>
+          <t xml:space="preserve">2030-02-17</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5A</t>
+          <t xml:space="preserve">Lyngevej 5C</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J270">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5C</t>
+          <t xml:space="preserve">Lyngevej 5E</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J271">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5E</t>
+          <t xml:space="preserve">Lyngevej 5G</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J272">
@@ -20441,40 +20441,40 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngevej 5G</t>
+          <t xml:space="preserve">Hovedgaden 75A</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t xml:space="preserve">8420</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">1450847</t>
+          <t xml:space="preserve">7216054</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J273">
-        <v>120</v>
+        <v>1923</v>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311423046</t>
+          <t xml:space="preserve">311434528</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-17</t>
+          <t xml:space="preserve">2030-02-24</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 75A</t>
+          <t xml:space="preserve">Hovedgaden 77</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20531,15 +20531,15 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J274">
-        <v>1923</v>
+        <v>3084</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311434528</t>
+          <t xml:space="preserve">311424218</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20591,40 +20591,40 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 77</t>
+          <t xml:space="preserve">Rosenholmvej 46</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">7216054</t>
+          <t xml:space="preserve">4149286</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J275">
-        <v>3084</v>
+        <v>152</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424218</t>
+          <t xml:space="preserve">311426611</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Factum2 A/S</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-02-24</t>
+          <t xml:space="preserve">2030-03-06</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,17 +20666,17 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 46</t>
+          <t xml:space="preserve">Lykkesholmvej 5A</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8444</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">4149286</t>
+          <t xml:space="preserve">4176833</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -20685,21 +20685,21 @@
         </is>
       </c>
       <c r="J276">
-        <v>152</v>
+        <v>60</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311426611</t>
+          <t xml:space="preserve">311430708</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Factum2 A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-06</t>
+          <t xml:space="preserve">2030-03-30</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lykkesholmvej 5A</t>
+          <t xml:space="preserve">Lykkesholmvej 5B</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20756,7 +20756,7 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J277">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lykkesholmvej 5B</t>
+          <t xml:space="preserve">Lykkesholmvej 5C</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20831,7 +20831,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J278">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lykkesholmvej 5C</t>
+          <t xml:space="preserve">Lykkesholmvej 5D</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -20906,7 +20906,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J279">
@@ -20966,40 +20966,40 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lykkesholmvej 5D</t>
+          <t xml:space="preserve">Tingvej 20</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t xml:space="preserve">8444</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">4176833</t>
+          <t xml:space="preserve">4148894</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J280">
-        <v>60</v>
+        <v>215</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311430708</t>
+          <t xml:space="preserve">311446325</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">H17 Ingeniørfirma ApS</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-03-30</t>
+          <t xml:space="preserve">2030-06-26</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -21041,17 +21041,17 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 20</t>
+          <t xml:space="preserve">Kirkevej 13</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148894</t>
+          <t xml:space="preserve">4151141</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -21060,21 +21060,21 @@
         </is>
       </c>
       <c r="J281">
-        <v>215</v>
+        <v>2309</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311446325</t>
+          <t xml:space="preserve">311448357</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t xml:space="preserve">H17 Ingeniørfirma ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-26</t>
+          <t xml:space="preserve">2030-07-07</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -21131,11 +21131,11 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J282">
-        <v>2309</v>
+        <v>583</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
@@ -21206,11 +21206,11 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J283">
-        <v>583</v>
+        <v>996</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
@@ -21281,11 +21281,11 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J284">
-        <v>996</v>
+        <v>960</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
@@ -21341,30 +21341,30 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 13</t>
+          <t xml:space="preserve">Hovedgaden 69A</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151141</t>
+          <t xml:space="preserve">4141859</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J285">
-        <v>960</v>
+        <v>129</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311448357</t>
+          <t xml:space="preserve">311454198</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-07-07</t>
+          <t xml:space="preserve">2030-08-13</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69A</t>
+          <t xml:space="preserve">Hovedgaden 69C</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21431,11 +21431,11 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="J286">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69C</t>
+          <t xml:space="preserve">Hovedgaden 69E</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -21506,15 +21506,15 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J287">
-        <v>132</v>
+        <v>369</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311454198</t>
+          <t xml:space="preserve">311454197</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69E</t>
+          <t xml:space="preserve">Hovedgaden 69F</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -21581,15 +21581,15 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">35</t>
         </is>
       </c>
       <c r="J288">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311454197</t>
+          <t xml:space="preserve">311454196</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69F</t>
+          <t xml:space="preserve">Hovedgaden 69G</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
@@ -21656,15 +21656,15 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J289">
-        <v>357</v>
+        <v>132</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311454196</t>
+          <t xml:space="preserve">311454198</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69G</t>
+          <t xml:space="preserve">Hovedgaden 69K</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
@@ -21731,11 +21731,11 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">24</t>
         </is>
       </c>
       <c r="J290">
-        <v>132</v>
+        <v>262</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
@@ -21791,7 +21791,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 69K</t>
+          <t xml:space="preserve">Hovedgaden 71A</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
@@ -21806,11 +21806,11 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J291">
-        <v>262</v>
+        <v>132</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
@@ -21866,7 +21866,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 71A</t>
+          <t xml:space="preserve">Hovedgaden 71C</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J292">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 71C</t>
+          <t xml:space="preserve">Hovedgaden 71E</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21956,11 +21956,11 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J293">
-        <v>132</v>
+        <v>262</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 71E</t>
+          <t xml:space="preserve">Hovedgaden 71K</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -22031,11 +22031,11 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J294">
-        <v>262</v>
+        <v>197</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 71K</t>
+          <t xml:space="preserve">Hovedgaden 71P</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22106,11 +22106,11 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J295">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 71P</t>
+          <t xml:space="preserve">Hovedgaden 79</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
@@ -22176,20 +22176,20 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141859</t>
+          <t xml:space="preserve">4141547</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J296">
-        <v>262</v>
+        <v>4455</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311454198</t>
+          <t xml:space="preserve">311476580</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -22199,7 +22199,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-08-13</t>
+          <t xml:space="preserve">2030-11-18</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,40 +22241,40 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 79</t>
+          <t xml:space="preserve">Kirkegade 30A</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141547</t>
+          <t xml:space="preserve">375855, 375856</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J297">
-        <v>4455</v>
+        <v>666</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476580</t>
+          <t xml:space="preserve">311551602</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-18</t>
+          <t xml:space="preserve">2031-09-29</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 30A</t>
+          <t xml:space="preserve">Nørreport 4A</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22326,20 +22326,20 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">375855, 375856</t>
+          <t xml:space="preserve">7140689</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J298">
-        <v>666</v>
+        <v>1016</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551602</t>
+          <t xml:space="preserve">311551603</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 4A</t>
+          <t xml:space="preserve">Nørreport 4B</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -22406,15 +22406,15 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J299">
-        <v>1016</v>
+        <v>2275</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551603</t>
+          <t xml:space="preserve">311551853</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 4B</t>
+          <t xml:space="preserve">Nørreport 4D</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -22481,15 +22481,15 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J300">
-        <v>2275</v>
+        <v>553</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551853</t>
+          <t xml:space="preserve">311551854</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 4D</t>
+          <t xml:space="preserve">Nørreport 4G</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -22556,15 +22556,15 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J301">
-        <v>553</v>
+        <v>438</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551854</t>
+          <t xml:space="preserve">311551855</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 4G</t>
+          <t xml:space="preserve">Nørreport 2</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -22626,20 +22626,20 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">7140689</t>
+          <t xml:space="preserve">375845, 375846, 375847, 375848</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J302">
-        <v>438</v>
+        <v>1260</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311551855</t>
+          <t xml:space="preserve">311561556</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-29</t>
+          <t xml:space="preserve">2031-11-12</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørreport 2</t>
+          <t xml:space="preserve">Østeralle 19</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -22701,30 +22701,30 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t xml:space="preserve">375845, 375846, 375847, 375848</t>
+          <t xml:space="preserve">5617696</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J303">
-        <v>1260</v>
+        <v>80</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561556</t>
+          <t xml:space="preserve">311630904</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thoudal Rådgivende Ingeniørfirma ApS</t>
+          <t xml:space="preserve">Murbyg ApS</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-12</t>
+          <t xml:space="preserve">2032-09-26</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -22766,40 +22766,40 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østeralle 19</t>
+          <t xml:space="preserve">Ballesvej 6</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8543</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">5617696</t>
+          <t xml:space="preserve">4148552</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J304">
-        <v>80</v>
+        <v>624</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311630904</t>
+          <t xml:space="preserve">311654004</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Murbyg ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-26</t>
+          <t xml:space="preserve">2033-01-13</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -22856,15 +22856,15 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J305">
-        <v>624</v>
+        <v>832</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654004</t>
+          <t xml:space="preserve">311657185</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-13</t>
+          <t xml:space="preserve">2033-01-31</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -22901,12 +22901,12 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syddjurs Kommune</t>
+          <t xml:space="preserve">Boligselskabet af 2014</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -22916,40 +22916,40 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ballesvej 6</t>
+          <t xml:space="preserve">Vestergade 114A</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">8543</t>
+          <t xml:space="preserve">8550</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">4148552</t>
+          <t xml:space="preserve">378677, 378678</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J306">
-        <v>832</v>
+        <v>636</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311657185</t>
+          <t xml:space="preserve">311666487</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-31</t>
+          <t xml:space="preserve">2033-03-15</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 114A</t>
+          <t xml:space="preserve">Vestergade 114B</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -23006,11 +23006,11 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J307">
-        <v>636</v>
+        <v>1725</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boligselskabet af 2014</t>
+          <t xml:space="preserve">djursBO</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -23066,30 +23066,30 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 114B</t>
+          <t xml:space="preserve">Bryggerivej 4</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">8550</t>
+          <t xml:space="preserve">8400</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">378677, 378678</t>
+          <t xml:space="preserve">374045, 374046, 374047</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J308">
-        <v>1725</v>
+        <v>1047</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311666487</t>
+          <t xml:space="preserve">311678041</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-15</t>
+          <t xml:space="preserve">2033-05-02</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -23126,12 +23126,12 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t xml:space="preserve">djursBO</t>
+          <t xml:space="preserve">Syddjurs Kommune</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -23141,7 +23141,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggerivej 4</t>
+          <t xml:space="preserve">A. Knudsens Vej 6</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
@@ -23151,7 +23151,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">374045, 374046, 374047</t>
+          <t xml:space="preserve">5618869</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -23160,21 +23160,21 @@
         </is>
       </c>
       <c r="J309">
-        <v>1047</v>
+        <v>510</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678041</t>
+          <t xml:space="preserve">311683327</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-02</t>
+          <t xml:space="preserve">2033-05-25</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -23201,12 +23201,12 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syddjurs Kommune</t>
+          <t xml:space="preserve">djursBO</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">A. Knudsens Vej 6</t>
+          <t xml:space="preserve">Søhusvej 8</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
@@ -23226,7 +23226,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">5618869</t>
+          <t xml:space="preserve">375867, 375868</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -23235,21 +23235,21 @@
         </is>
       </c>
       <c r="J310">
-        <v>510</v>
+        <v>5651</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683327</t>
+          <t xml:space="preserve">311690706</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-25</t>
+          <t xml:space="preserve">2033-06-26</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søhusvej 8</t>
+          <t xml:space="preserve">Søhusvej 8F</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
@@ -23301,20 +23301,20 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">375867, 375868</t>
+          <t xml:space="preserve">412342, 412343</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J311">
-        <v>5651</v>
+        <v>3383</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690706</t>
+          <t xml:space="preserve">311690710</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -23351,12 +23351,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t xml:space="preserve">djursBO</t>
+          <t xml:space="preserve">Syddjurs Kommune</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -23366,40 +23366,40 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søhusvej 8F</t>
+          <t xml:space="preserve">Kirkevej 13A</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t xml:space="preserve">8400</t>
+          <t xml:space="preserve">8544</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">412342, 412343</t>
+          <t xml:space="preserve">4151141</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J312">
-        <v>3383</v>
+        <v>1066</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311690710</t>
+          <t xml:space="preserve">311700070</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-06-26</t>
+          <t xml:space="preserve">2033-08-15</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -23426,12 +23426,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Syddjurs Kommune</t>
+          <t xml:space="preserve">djursBO</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -23441,40 +23441,40 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkevej 13A</t>
+          <t xml:space="preserve">Bugtrupvej 16A</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">8544</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">4151141</t>
+          <t xml:space="preserve">378632, 378633</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J313">
-        <v>1066</v>
+        <v>968</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">311700070</t>
+          <t xml:space="preserve">311735942</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-15</t>
+          <t xml:space="preserve">2034-01-30</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -23501,12 +23501,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t xml:space="preserve">djursBO</t>
+          <t xml:space="preserve">Syddjurs Kommune</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -23516,40 +23516,40 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bugtrupvej 16A</t>
+          <t xml:space="preserve">Fiskegårdevej 3A</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">8560</t>
+          <t xml:space="preserve">8444</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">378632, 378633</t>
+          <t xml:space="preserve">4173743</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J314">
-        <v>968</v>
+        <v>753</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311735942</t>
+          <t xml:space="preserve">311812523</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-30</t>
+          <t xml:space="preserve">2035-02-19</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiskegårdevej 3A</t>
+          <t xml:space="preserve">Fiskegårdevej 3B</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -23606,15 +23606,15 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J315">
-        <v>753</v>
+        <v>890</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812523</t>
+          <t xml:space="preserve">311812524</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23666,30 +23666,30 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fiskegårdevej 3B</t>
+          <t xml:space="preserve">Lerbakken 21</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">8444</t>
+          <t xml:space="preserve">8410</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">4173743</t>
+          <t xml:space="preserve">4141156</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J316">
-        <v>890</v>
+        <v>629</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812524</t>
+          <t xml:space="preserve">311812521</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23741,40 +23741,40 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lerbakken 21</t>
+          <t xml:space="preserve">Frellingvej 8</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410</t>
+          <t xml:space="preserve">8560</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">4141156</t>
+          <t xml:space="preserve">10043845</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J317">
-        <v>629</v>
+        <v>99</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311812521</t>
+          <t xml:space="preserve">311929040</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-02-19</t>
+          <t xml:space="preserve">2036-09-30</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189978.xlsx
+++ b/public/exports-from-60-with-coowners/29189978.xlsx
@@ -9139,7 +9139,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">310000943</t>
+          <t xml:space="preserve">310000942</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294471</t>
+          <t xml:space="preserve">311294470</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311294465</t>
+          <t xml:space="preserve">311294461</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -18139,12 +18139,12 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311411362</t>
+          <t xml:space="preserve">311411363</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M242" t="inlineStr">
